--- a/kurva_pertumbuhan/Pontianak/male/zscore_tb_male.xlsx
+++ b/kurva_pertumbuhan/Pontianak/male/zscore_tb_male.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D381"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5416,1806 +5416,6 @@
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282">
-        <v>17.1</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C282">
-        <v>154.4726924194111</v>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283">
-        <v>17.1</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C283">
-        <v>160.3523247137847</v>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284">
-        <v>17.1</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C284">
-        <v>166.5470357705002</v>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285">
-        <v>17.1</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C285">
-        <v>172.7341985345436</v>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286">
-        <v>17.1</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C286">
-        <v>178.5927158968564</v>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287">
-        <v>17.2</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C287">
-        <v>154.6464565523769</v>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288">
-        <v>17.2</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C288">
-        <v>160.4432907700468</v>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289">
-        <v>17.2</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C289">
-        <v>166.5659940802448</v>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290">
-        <v>17.2</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C290">
-        <v>172.6963221145199</v>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291">
-        <v>17.2</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C291">
-        <v>178.5144803649287</v>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292">
-        <v>17.3</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C292">
-        <v>154.815408637754</v>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293">
-        <v>17.3</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C293">
-        <v>160.5311147759895</v>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294">
-        <v>17.3</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C294">
-        <v>166.5827558315196</v>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295">
-        <v>17.3</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C295">
-        <v>172.6565414789831</v>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296">
-        <v>17.3</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C296">
-        <v>178.4341676019342</v>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297">
-        <v>17.4</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C297">
-        <v>154.981810117543</v>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298">
-        <v>17.4</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C298">
-        <v>160.6181051478526</v>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299">
-        <v>17.4</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C299">
-        <v>166.5997042349063</v>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300">
-        <v>17.4</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C300">
-        <v>172.6173225435257</v>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301">
-        <v>17.4</v>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C301">
-        <v>178.3543173224409</v>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302">
-        <v>17.5</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C302">
-        <v>155.1470824201271</v>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303">
-        <v>17.5</v>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C303">
-        <v>160.7056865878932</v>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304">
-        <v>17.5</v>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C304">
-        <v>166.6182987988673</v>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305">
-        <v>17.5</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C305">
-        <v>172.5801746384682</v>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306">
-        <v>17.5</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C306">
-        <v>178.2764881956484</v>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307">
-        <v>17.6</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C307">
-        <v>155.3119391792756</v>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308">
-        <v>17.6</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C308">
-        <v>160.7945422175007</v>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309">
-        <v>17.6</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C309">
-        <v>166.6392256588007</v>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310">
-        <v>17.6</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C310">
-        <v>172.5458070013591</v>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311">
-        <v>17.6</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C311">
-        <v>178.2014185998104</v>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312">
-        <v>17.7</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C312">
-        <v>155.4770717485573</v>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313">
-        <v>17.7</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C313">
-        <v>160.8853327874392</v>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314">
-        <v>17.7</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C314">
-        <v>166.6631470976444</v>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315">
-        <v>17.7</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C315">
-        <v>172.5149033277599</v>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316">
-        <v>17.7</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C316">
-        <v>178.129820163472</v>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317">
-        <v>17.8</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C317">
-        <v>155.6431616005972</v>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318">
-        <v>17.8</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C318">
-        <v>160.9787097301804</v>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319">
-        <v>17.8</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C319">
-        <v>166.6907152099733</v>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320">
-        <v>17.8</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C320">
-        <v>172.4881358929353</v>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321">
-        <v>17.8</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C321">
-        <v>178.0623921652343</v>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322">
-        <v>17.9</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C322">
-        <v>155.8103273188673</v>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323">
-        <v>17.9</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C323">
-        <v>161.0747419221513</v>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324">
-        <v>17.9</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C324">
-        <v>166.7219780614299</v>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325">
-        <v>17.9</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C325">
-        <v>172.4655518274442</v>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326">
-        <v>17.9</v>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C326">
-        <v>177.9991896398353</v>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327">
-        <v>18</v>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C327">
-        <v>155.9778161175707</v>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328">
-        <v>18</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C328">
-        <v>161.1725976374951</v>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329">
-        <v>18</v>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C329">
-        <v>166.7560516303756</v>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330">
-        <v>18</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C330">
-        <v>172.4462351123671</v>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331">
-        <v>18</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C331">
-        <v>177.939276039721</v>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332">
-        <v>18.1</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C332">
-        <v>156.1447907239829</v>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333">
-        <v>18.1</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C333">
-        <v>161.271361574837</v>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334">
-        <v>18.1</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C334">
-        <v>166.7919674729276</v>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335">
-        <v>18.1</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C335">
-        <v>172.4291835908134</v>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336">
-        <v>18.1</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C336">
-        <v>177.8816268284621</v>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337">
-        <v>18.2</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C337">
-        <v>156.3104257731532</v>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338">
-        <v>18.2</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C338">
-        <v>161.3701346929161</v>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339">
-        <v>18.2</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C339">
-        <v>166.8287761489808</v>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340">
-        <v>18.2</v>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C340">
-        <v>172.413415854051</v>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341">
-        <v>18.2</v>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C341">
-        <v>177.8252394851914</v>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342">
-        <v>18.3</v>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C342">
-        <v>156.4739776715914</v>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343">
-        <v>18.3</v>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C343">
-        <v>161.4681065182606</v>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344">
-        <v>18.3</v>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C344">
-        <v>166.865622000292</v>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345">
-        <v>18.3</v>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C345">
-        <v>172.3980482816426</v>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346">
-        <v>18.3</v>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C346">
-        <v>177.7692124425825</v>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347">
-        <v>18.4</v>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C347">
-        <v>156.6350515710013</v>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348">
-        <v>18.4</v>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C348">
-        <v>161.5648316431185</v>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349">
-        <v>18.4</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C349">
-        <v>166.9020290856435</v>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350">
-        <v>18.4</v>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C350">
-        <v>172.3825896338787</v>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351">
-        <v>18.4</v>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C351">
-        <v>177.7130470524726</v>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352">
-        <v>18.5</v>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C352">
-        <v>156.7933068160928</v>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353">
-        <v>18.5</v>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C353">
-        <v>161.6599230945248</v>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354">
-        <v>18.5</v>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C354">
-        <v>166.937583039392</v>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355">
-        <v>18.5</v>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C355">
-        <v>172.3666126630548</v>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356">
-        <v>18.5</v>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C356">
-        <v>177.65631067557</v>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357">
-        <v>18.6</v>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C357">
-        <v>156.9483999204322</v>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358">
-        <v>18.6</v>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C358">
-        <v>161.7529929616864</v>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359">
-        <v>18.6</v>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C359">
-        <v>166.9718694959218</v>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360">
-        <v>18.6</v>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C360">
-        <v>172.3496905838776</v>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361">
-        <v>18.6</v>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C361">
-        <v>177.5985715243027</v>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362">
-        <v>18.7</v>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C362">
-        <v>157.100060032521</v>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363">
-        <v>18.7</v>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C363">
-        <v>161.843729216523</v>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364">
-        <v>18.7</v>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C364">
-        <v>167.0045530221536</v>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365">
-        <v>18.7</v>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C365">
-        <v>172.3314788353747</v>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366">
-        <v>18.7</v>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C366">
-        <v>177.5394838104614</v>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367">
-        <v>18.8</v>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C367">
-        <v>157.2484622139616</v>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368">
-        <v>18.8</v>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C368">
-        <v>161.9322759643868</v>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369">
-        <v>18.8</v>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C369">
-        <v>167.0357677353552</v>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370">
-        <v>18.8</v>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C370">
-        <v>172.3121194373487</v>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371">
-        <v>18.8</v>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C371">
-        <v>177.4792085404241</v>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372">
-        <v>18.9</v>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C372">
-        <v>157.3939450366593</v>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373">
-        <v>18.9</v>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C373">
-        <v>162.0189453595386</v>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374">
-        <v>18.9</v>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C374">
-        <v>167.0658206854532</v>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375">
-        <v>18.9</v>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C375">
-        <v>172.2919330317814</v>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376">
-        <v>18.9</v>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C376">
-        <v>177.4180920495578</v>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377">
-        <v>19</v>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Z-2</t>
-        </is>
-      </c>
-      <c r="C377">
-        <v>157.5368459819323</v>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378">
-        <v>19</v>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Z-1</t>
-        </is>
-      </c>
-      <c r="C378">
-        <v>162.1040497315066</v>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379">
-        <v>19</v>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Z0</t>
-        </is>
-      </c>
-      <c r="C379">
-        <v>167.095019192724</v>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380">
-        <v>19</v>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="C380">
-        <v>172.2712398910584</v>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381">
-        <v>19</v>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Z2</t>
-        </is>
-      </c>
-      <c r="C381">
-        <v>177.3564794450068</v>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>local_male_tb</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
